--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ОБЩИНА БЕЛОСЛАВ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,6 +61,18 @@
     <t>2026-05-04</t>
   </si>
   <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
     <t>А4699РМ</t>
   </si>
   <si>
@@ -67,10 +82,31 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>19:04</t>
-  </si>
-  <si>
-    <t>09:38</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>19:04:00</t>
+  </si>
+  <si>
+    <t>09:38:00</t>
+  </si>
+  <si>
+    <t>15:55:00</t>
+  </si>
+  <si>
+    <t>09:03:00</t>
+  </si>
+  <si>
+    <t>3231412761 3231412761</t>
+  </si>
+  <si>
+    <t>3231416180 3231416180</t>
+  </si>
+  <si>
+    <t>3231950624 3231950624</t>
+  </si>
+  <si>
+    <t>3232456113 3232456113</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА БЕЛОСЛАВ</t>
@@ -494,24 +530,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,160 +589,257 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1186</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>44.51</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>73.89</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.77</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>78.78</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>23800</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>1186</v>
-      </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>45.75</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>75.94</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.77</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>80.98</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="L3">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>55.45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>1.7</v>
+      </c>
+      <c r="I4" s="1">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="J4">
+        <v>1.79</v>
+      </c>
+      <c r="K4" s="1">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>161862</v>
+      <c r="N4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>56.02</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>1.71</v>
+      </c>
+      <c r="I5" s="1">
+        <v>95.79000000000001</v>
+      </c>
+      <c r="J5">
+        <v>1.82</v>
+      </c>
+      <c r="K5" s="1">
+        <v>101.96</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
+      <c r="B10" s="6">
+        <v>201.73</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.6848</v>
+      </c>
+      <c r="E10" s="6">
+        <v>339.88</v>
+      </c>
+      <c r="F10" s="6">
+        <v>360.98</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6">
-        <v>90.26000000000001</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.66</v>
-      </c>
-      <c r="E8" s="6">
-        <v>149.83</v>
-      </c>
-      <c r="F8" s="6">
-        <v>159.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="9">
-        <v>90.26000000000001</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>149.83</v>
-      </c>
-      <c r="F9" s="9">
-        <v>159.76</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="9">
+        <v>201.73</v>
+      </c>
+      <c r="C11" s="9">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9">
+        <v>339.88</v>
+      </c>
+      <c r="F11" s="9">
+        <v>360.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -160,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,12 +170,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -225,17 +219,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,22 +52,28 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-16</t>
   </si>
   <si>
     <t>2026-06-19</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>A7353HC</t>
@@ -85,16 +94,31 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-06-16 07:02:34</t>
-  </si>
-  <si>
-    <t>2026-06-16 09:18:17</t>
-  </si>
-  <si>
-    <t>2026-06-16 23:18:52</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:42:41</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>07:02:00</t>
+  </si>
+  <si>
+    <t>:  :00</t>
+  </si>
+  <si>
+    <t>15:43:00</t>
+  </si>
+  <si>
+    <t>3233433537 3233433537</t>
+  </si>
+  <si>
+    <t>3233411965 3233411965</t>
+  </si>
+  <si>
+    <t>3233478076 3233478076</t>
+  </si>
+  <si>
+    <t>3233598527 3233598527</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА БЕЛОСЛАВ</t>
@@ -512,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,14 +545,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,150 +589,192 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2">
+        <v>23.16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>1.44</v>
+      </c>
+      <c r="I2" s="1">
+        <v>33.35</v>
+      </c>
+      <c r="J2">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="1">
+        <v>36.13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
         <v>40.13</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I3" s="1">
         <v>57.79</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K3" s="1">
         <v>62.6</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>23.16</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H3">
-        <v>33.35</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J3">
-        <v>36.13</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
       </c>
       <c r="F4">
         <v>32.05</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4">
         <v>1.44</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>46.15</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>50</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
       </c>
       <c r="F5">
         <v>19.31</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
         <v>1.7</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>32.83</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>34.76</v>
       </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -713,29 +782,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6">
         <v>95.34</v>
@@ -753,9 +822,9 @@
         <v>148.73</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6">
         <v>19.31</v>
@@ -773,9 +842,9 @@
         <v>34.76</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B12" s="9">
         <v>114.65</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -106,7 +106,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <v>1.3799</v>
+        <v>1.379915</v>
       </c>
       <c r="E7" s="6">
         <v>58.26</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -497,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -510,13 +513,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,54 +562,60 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>42.22</v>
+        <v>42.222</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>1.38</v>
+        <v>1.379</v>
       </c>
       <c r="I2" s="1">
-        <v>58.26</v>
+        <v>1.379</v>
       </c>
       <c r="J2">
+        <v>58.224138</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.53</v>
       </c>
-      <c r="K2" s="1">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>64.59966</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>21</v>
+      <c r="O2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -614,59 +623,59 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6">
-        <v>42.22</v>
+        <v>42.222</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <v>1.379915</v>
+        <v>1.379</v>
       </c>
       <c r="E7" s="6">
-        <v>58.26</v>
+        <v>58.22</v>
       </c>
       <c r="F7" s="6">
         <v>64.59999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="9">
-        <v>42.22</v>
+        <v>42.222</v>
       </c>
       <c r="C8" s="9">
         <v>1</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="9">
-        <v>58.26</v>
+        <v>58.22</v>
       </c>
       <c r="F8" s="9">
         <v>64.59999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -108,8 +105,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -202,10 +199,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -513,13 +510,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,60 +559,54 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>42.222</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>1.379</v>
       </c>
       <c r="I2" s="1">
-        <v>1.379</v>
+        <v>58.224</v>
       </c>
       <c r="J2">
-        <v>58.224138</v>
+        <v>1.53</v>
       </c>
       <c r="K2" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L2" s="1">
-        <v>64.59966</v>
-      </c>
-      <c r="M2" t="s">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
         <v>21</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -623,49 +614,49 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6">
         <v>42.222</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="7">
         <v>1.379</v>
       </c>
-      <c r="E7" s="6">
-        <v>58.22</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="7">
+        <v>58.224</v>
+      </c>
+      <c r="F7" s="7">
         <v>64.59999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9">
         <v>42.222</v>
@@ -675,7 +666,7 @@
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="9">
-        <v>58.22</v>
+        <v>58.224</v>
       </c>
       <c r="F8" s="9">
         <v>64.59999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА БЕЛОСЛАВ/ОБЩИНА БЕЛОСЛАВ.xlsx
@@ -628,10 +628,10 @@
         <v>27</v>
       </c>
       <c r="H2" s="1">
-        <v>1.686</v>
+        <v>1.69</v>
       </c>
       <c r="I2" s="1">
-        <v>102.424</v>
+        <v>102.667</v>
       </c>
       <c r="J2" s="1">
         <v>1.81</v>
@@ -672,10 +672,10 @@
         <v>27</v>
       </c>
       <c r="H3" s="1">
-        <v>1.686</v>
+        <v>1.69</v>
       </c>
       <c r="I3" s="1">
-        <v>68.974</v>
+        <v>69.13800000000001</v>
       </c>
       <c r="J3" s="1">
         <v>1.81</v>
@@ -716,10 +716,10 @@
         <v>27</v>
       </c>
       <c r="H4" s="1">
-        <v>1.439</v>
+        <v>1.44</v>
       </c>
       <c r="I4" s="1">
-        <v>83.505</v>
+        <v>83.563</v>
       </c>
       <c r="J4" s="1">
         <v>1.55</v>
@@ -760,10 +760,10 @@
         <v>27</v>
       </c>
       <c r="H5" s="1">
-        <v>1.489</v>
+        <v>1.49</v>
       </c>
       <c r="I5" s="1">
-        <v>70.087</v>
+        <v>70.134</v>
       </c>
       <c r="J5" s="1">
         <v>1.61</v>
@@ -822,10 +822,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.46139</v>
+        <v>1.46239</v>
       </c>
       <c r="E10" s="6">
-        <v>153.59</v>
+        <v>153.7</v>
       </c>
       <c r="F10" s="6">
         <v>165.73</v>
@@ -842,10 +842,10 @@
         <v>2</v>
       </c>
       <c r="D11" s="8">
-        <v>1.68599</v>
+        <v>1.69</v>
       </c>
       <c r="E11" s="6">
-        <v>171.4</v>
+        <v>171.8</v>
       </c>
       <c r="F11" s="6">
         <v>184</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="10">
-        <v>324.99</v>
+        <v>325.5</v>
       </c>
       <c r="F12" s="10">
         <v>349.73</v>
